--- a/etf_holdings/2026-09-01_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.62%2405</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2405</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.09%5485</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.09%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5485</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.93%3425</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.93%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>3425</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-10%999</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-10%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>999</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.51%3925</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.51%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3925</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.46%7095</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.46%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>7095</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+3.54%5990</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+3.54%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>5990</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.71%545</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.71%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>545</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.55%1840</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.55%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1840</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-4.24%2035</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-4.24%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>2035</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.99%5130</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.99%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>5130</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.81%1230</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.81%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1230</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.77%129</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.77%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>129</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-5.96%584</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.96%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>584</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:57</t>
+          <t>2026-09-01 15:28:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.98%2170</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.98%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2170</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,17 +1454,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-3.69%1435</t>
+          <t>+1.05%1450</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.69%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1452,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1487,17 +1517,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.71%2305</t>
+          <t>-0.87%2285</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1515,7 +1545,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1550,17 +1580,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+2.78%16065</t>
+          <t>+6.57%17120</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>+6.57%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>17120</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1578,7 +1608,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,17 +1643,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-4.81%257</t>
+          <t>+8.56%279</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-4.81%</t>
+          <t>+8.56%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>279</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1641,7 +1671,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,17 +1706,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.12%969</t>
+          <t>+2.17%990</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>990</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1704,7 +1734,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,17 +1769,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+1.41%6100</t>
+          <t>-1.72%5995</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1767,7 +1797,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,17 +1832,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.16%609</t>
+          <t>-1.48%600</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1830,7 +1860,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1865,17 +1895,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+3.1%1165</t>
+          <t>+5.15%1225</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>+5.15%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1893,7 +1923,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1928,12 +1958,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-7.11%1175</t>
+          <t>0%1175</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-7.11%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1956,7 +1986,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1991,17 +2021,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.98%228</t>
+          <t>+4.17%237.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.98%</t>
+          <t>+4.17%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>237.5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2019,7 +2049,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2054,17 +2084,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+6.16%2845</t>
+          <t>+9.84%3125</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+9.84%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2082,7 +2112,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2117,17 +2147,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+4.06%500</t>
+          <t>+7%535</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+4.06%</t>
+          <t>+7%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>535</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2145,7 +2175,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2180,17 +2210,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.99%199.5</t>
+          <t>+0.25%200</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2208,7 +2238,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:30:58</t>
+          <t>2026-09-01 15:28:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2243,17 +2273,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.4%212</t>
+          <t>+8.96%231</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+8.96%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>231</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2271,7 +2301,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2306,16 +2336,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.38%214</t>
+          <t>-0.47%213</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2367,16 +2397,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.18%83.7</t>
+          <t>+0.72%84.3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>83.7</v>
+        <v>84.3</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2393,7 +2423,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2428,16 +2458,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+3.11%248.5</t>
+          <t>+1.41%252</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+3.11%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>248.5</v>
+        <v>252</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2489,16 +2519,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.52%18.95</t>
+          <t>+0.53%19.05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>18.95</v>
+        <v>19.05</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2515,7 +2545,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2550,16 +2580,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.55%540</t>
+          <t>-2.59%526</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-2.59%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2611,16 +2641,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.25%4075</t>
+          <t>+4.91%4275</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+4.91%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>4075</v>
+        <v>4275</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2672,16 +2702,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.38%78.8</t>
+          <t>-0.25%78.6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>78.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2733,16 +2763,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.71%1425</t>
+          <t>+1.4%1445</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1425</v>
+        <v>1445</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2794,16 +2824,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+8.28%7650</t>
+          <t>-0.92%7580</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+8.28%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>7650</v>
+        <v>7580</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2855,16 +2885,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.8%338.5</t>
+          <t>+1.03%342</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>338.5</v>
+        <v>342</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2916,16 +2946,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.47%1345</t>
+          <t>+2.23%1375</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+2.23%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1345</v>
+        <v>1375</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2977,16 +3007,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.56%543</t>
+          <t>-4.6%518</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,16 +3068,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+2.17%94.1</t>
+          <t>+1.59%95.6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+1.59%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>94.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3099,16 +3129,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.56%6285</t>
+          <t>+9.94%6910</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6285</v>
+        <v>6910</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:00</t>
+          <t>2026-09-01 15:28:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3160,16 +3190,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.49%1960</t>
+          <t>+3.57%2030</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+3.57%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1960</v>
+        <v>2030</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:01</t>
+          <t>2026-09-01 15:28:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3221,16 +3251,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-6.17%912</t>
+          <t>+8.99%994</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-6.17%</t>
+          <t>+8.99%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>912</v>
+        <v>994</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:01</t>
+          <t>2026-09-01 15:28:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3282,16 +3312,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.03%578</t>
+          <t>+0.35%580</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:01</t>
+          <t>2026-09-01 15:28:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3343,16 +3373,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-1.55%89.1</t>
+          <t>+4.6%93.2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-1.55%</t>
+          <t>+4.6%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>89.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:01</t>
+          <t>2026-09-01 15:28:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3404,16 +3434,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.19%250</t>
+          <t>+2.4%256</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:01</t>
+          <t>2026-09-01 15:28:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3465,16 +3495,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.98%151.5</t>
+          <t>+1.32%153.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>151.5</v>
+        <v>153.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:31:01</t>
+          <t>2026-09-01 15:28:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3526,16 +3556,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-1.95%151</t>
+          <t>+3.97%157</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+3.97%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-01_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.46%2440</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.46%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2440</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.83%5640</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.83%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5640</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.44%3410</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.44%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3410</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.8%971</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.8%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>971</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+9.94%4315</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+9.94%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>4315</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+9.94%7800</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+9.94%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>7800</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.51%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.75%5885</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.75%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5885</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+4.22%568</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+4.22%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>568</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.36%1865</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.36%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1865</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+8.35%2205</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+8.35%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2205</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.46%5410</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.46%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5410</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.41%1225</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1225</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.71%132.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.71%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>132.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+4.45%610</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+4.45%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>610</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:14</t>
+          <t>2026-09-01 15:55:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+6.68%2315</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+6.68%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2315</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:20</t>
+          <t>2026-09-01 15:55:11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:21</t>
+          <t>2026-09-01 15:55:12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:23</t>
+          <t>2026-09-01 15:55:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:23</t>
+          <t>2026-09-01 15:55:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:23</t>
+          <t>2026-09-01 15:55:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:23</t>
+          <t>2026-09-01 15:55:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:23</t>
+          <t>2026-09-01 15:55:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:23</t>
+          <t>2026-09-01 15:55:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:08</t>
+          <t>2026-09-01 16:12:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:11</t>
+          <t>2026-09-01 16:12:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:12</t>
+          <t>2026-09-01 16:12:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:14</t>
+          <t>2026-09-01 16:12:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:14</t>
+          <t>2026-09-01 16:12:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:14</t>
+          <t>2026-09-01 16:12:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:14</t>
+          <t>2026-09-01 16:12:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:14</t>
+          <t>2026-09-01 16:12:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:14</t>
+          <t>2026-09-01 16:12:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.46%2440</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2440</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.38%11,014,000</t>
+          <t>9.23%11,014,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.38%</t>
+          <t>9.23%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +572,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.83%5640</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+2.83%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5640</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.24%4,757,000</t>
+          <t>9.21%4,757,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.24%</t>
+          <t>9.21%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +630,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.44%3410</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.44%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>3410</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.21%5,949,000</t>
+          <t>7.54%5,088,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.21%</t>
+          <t>7.54%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5949000</v>
+        <v>5088000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +693,40 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.8%971</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>971</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.18%20,300,000</t>
+          <t>6.97%5,949,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.18%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>20300000</v>
+        <v>5949000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +756,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+9.94%4315</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+9.94%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>4315</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.07%5,088,000</t>
+          <t>6.77%20,300,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.07%</t>
+          <t>6.77%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5088000</v>
+        <v>20300000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +824,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+9.94%7800</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+9.94%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>7800</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.47%2,176,000</t>
+          <t>5.83%2,176,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.47%</t>
+          <t>5.83%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +882,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.75%5885</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.75%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>5885</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.08%2,397,000</t>
+          <t>4.89%6,464,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.08%</t>
+          <t>4.89%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2397000</v>
+        <v>6464000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +950,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+4.22%568</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+4.22%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>568</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.82%24,987,000</t>
+          <t>4.87%24,987,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>4.87%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +1008,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.36%1865</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.36%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1865</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.72%7,240,000</t>
+          <t>4.84%2,397,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>4.84%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7240000</v>
+        <v>2397000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1071,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+8.35%2205</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+8.35%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>2205</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.66%6,464,000</t>
+          <t>4.64%7,240,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.66%</t>
+          <t>4.64%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6464000</v>
+        <v>7240000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1139,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.46%5410</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+5.46%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>5410</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.50%2,476,000</t>
+          <t>4.60%2,476,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>4.60%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1197,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.41%1225</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.41%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1225</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.13%9,474,000</t>
+          <t>4.06%89,118,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.13%</t>
+          <t>4.06%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>9474000</v>
+        <v>89118000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1260,40 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+2.71%132.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+2.71%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>132.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.07%89,118,000</t>
+          <t>3.99%9,474,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>89118000</v>
+        <v>9474000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1328,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+4.45%610</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+4.45%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>610</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.86%18,679,000</t>
+          <t>3.91%18,679,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>3.91%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:51</t>
+          <t>2026-09-01 17:52:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1391,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+6.68%2315</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+6.68%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2315</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.53%4,591,848</t>
+          <t>3.65%4,591,848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1439,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.74%5,398,000</t>
+          <t>2.69%5,398,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1502,12 +1532,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.41%1,731,000</t>
+          <t>1.36%1,731,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1545,40 +1575,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+6.57%17120</t>
+          <t>+8.56%279</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+6.57%</t>
+          <t>+8.56%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17120</t>
+          <t>279</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.18%207,900</t>
+          <t>1.23%12,818,450</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>207900</v>
+        <v>12818450</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1608,40 +1638,40 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+8.56%279</t>
+          <t>+6.57%17120</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+8.56%</t>
+          <t>+6.57%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>17120</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.17%12,818,450</t>
+          <t>1.22%207,900</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>12818450</v>
+        <v>207900</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1754,12 +1784,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.70%325,000</t>
+          <t>0.67%325,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1797,40 +1827,40 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4979華星光</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.48%600</t>
+          <t>+5.15%1225</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>+5.15%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.68%3,173,000</t>
+          <t>0.61%1,457,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3173000</v>
+        <v>1457000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1860,40 +1890,40 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>4979華星光</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+5.15%1225</t>
+          <t>-1.48%600</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+5.15%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.60%1,457,000</t>
+          <t>0.58%2,838,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1457000</v>
+        <v>2838000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1943,12 +1973,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.54%1,300,000</t>
+          <t>0.52%1,300,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,40 +2016,40 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+4.17%237.5</t>
+          <t>+9.84%3125</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+4.17%</t>
+          <t>+9.84%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>237.5</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.48%5,916,000</t>
+          <t>0.51%477,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>5916000</v>
+        <v>477000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2049,27 +2079,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+9.84%3125</t>
+          <t>+4.17%237.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+9.84%</t>
+          <t>+4.17%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>237.5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.48%477,000</t>
+          <t>0.48%5,916,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2078,11 +2108,11 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>477000</v>
+        <v>5916000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2132,20 +2162,20 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.29%1,644,000</t>
+          <t>0.40%2,157,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1644000</v>
+        <v>2157000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2195,12 +2225,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.23%3,248,000</t>
+          <t>0.22%3,248,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:53</t>
+          <t>2026-09-01 17:52:26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2258,12 +2288,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.17%2,222,000</t>
+          <t>0.18%2,222,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2271,7 +2301,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2362,38 +2392,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6191精成科</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.72%84.3</t>
+          <t>+9.94%6910</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>84.3</v>
+        <v>6910</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.12%3,988,000</t>
+          <t>0.13%54,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>3988000</v>
+        <v>54000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2423,34 +2453,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>6191精成科</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.41%252</t>
+          <t>+0.72%84.3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>252</v>
+        <v>84.3</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.04%501,000</t>
+          <t>0.12%3,988,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>501000</v>
+        <v>3988000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2484,34 +2514,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2002中鋼</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.53%19.05</t>
+          <t>+1.41%252</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>19.05</v>
+        <v>252</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.03%5,163,000</t>
+          <t>0.04%501,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>5163000</v>
+        <v>501000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2545,34 +2575,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>2002中鋼</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-2.59%526</t>
+          <t>+0.53%19.05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2.59%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>526</v>
+        <v>19.05</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.03%5,163,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1000</v>
+        <v>5163000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2606,21 +2636,21 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+4.91%4275</t>
+          <t>-2.59%526</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+4.91%</t>
+          <t>-2.59%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>4275</v>
+        <v>526</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2667,21 +2697,21 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2439美律</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.25%78.6</t>
+          <t>+4.91%4275</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+4.91%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>78.59999999999999</v>
+        <v>4275</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2728,21 +2758,21 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1590亞德客-KY</t>
+          <t>2439美律</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+1.4%1445</t>
+          <t>-0.25%78.6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1445</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2789,21 +2819,21 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.92%7580</t>
+          <t>+1.4%1445</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>7580</v>
+        <v>1445</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2850,21 +2880,21 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2382廣達</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.03%342</t>
+          <t>-0.92%7580</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>342</v>
+        <v>7580</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2911,25 +2941,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>2382廣達</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+2.23%1375</t>
+          <t>+1.03%342</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1375</v>
+        <v>342</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0%8,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2938,7 +2968,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>8000</v>
+        <v>1000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2972,25 +3002,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-4.6%518</t>
+          <t>+2.23%1375</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>+2.23%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>518</v>
+        <v>1375</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0%8,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2999,7 +3029,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3033,21 +3063,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2637慧洋-KY</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+1.59%95.6</t>
+          <t>-4.6%518</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+1.59%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>95.59999999999999</v>
+        <v>518</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3094,21 +3124,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>2637慧洋-KY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+9.94%6910</t>
+          <t>+1.59%95.6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+1.59%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6910</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:54</t>
+          <t>2026-09-01 17:52:27</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:55</t>
+          <t>2026-09-01 17:52:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:55</t>
+          <t>2026-09-01 17:52:29</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:55</t>
+          <t>2026-09-01 17:52:29</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:55</t>
+          <t>2026-09-01 17:52:29</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:55</t>
+          <t>2026-09-01 17:52:29</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 16:12:55</t>
+          <t>2026-09-01 17:52:29</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.46%2440</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.46%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2440</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.83%5640</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.83%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5640</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+9.94%4315</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+9.94%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4315</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.44%3410</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.44%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3410</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.8%971</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.8%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>971</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+9.94%7800</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+9.94%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>7800</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+8.35%2205</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+8.35%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2205</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+4.22%568</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+4.22%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>568</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.75%5885</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.75%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5885</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.36%1865</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.36%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1865</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.46%5410</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.46%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5410</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.71%132.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.71%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>132.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.41%1225</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1225</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+4.45%610</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+4.45%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>610</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:21</t>
+          <t>2026-09-01 19:34:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+6.68%2315</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+6.68%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2315</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:26</t>
+          <t>2026-09-01 19:34:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:27</t>
+          <t>2026-09-01 19:34:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:29</t>
+          <t>2026-09-01 19:34:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:29</t>
+          <t>2026-09-01 19:34:24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:29</t>
+          <t>2026-09-01 19:34:24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:29</t>
+          <t>2026-09-01 19:34:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:29</t>
+          <t>2026-09-01 19:34:24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 17:52:29</t>
+          <t>2026-09-01 19:34:24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.46%2440</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2440</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.83%5640</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+2.83%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5640</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+9.94%4315</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+9.94%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4315</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.44%3410</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.44%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3410</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.8%971</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>971</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+9.94%7800</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+9.94%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>7800</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+8.35%2205</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+8.35%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>2205</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+4.22%568</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+4.22%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>568</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.75%5885</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.75%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>5885</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.36%1865</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.36%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1865</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.46%5410</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+5.46%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>5410</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.71%132.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.71%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>132.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.41%1225</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.41%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1225</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+4.45%610</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+4.45%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>610</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:17</t>
+          <t>2026-09-01 20:32:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+6.68%2315</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+6.68%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2315</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:21</t>
+          <t>2026-09-01 20:32:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:23</t>
+          <t>2026-09-01 20:32:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:24</t>
+          <t>2026-09-01 20:33:08</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:24</t>
+          <t>2026-09-01 20:33:08</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:24</t>
+          <t>2026-09-01 20:33:08</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:24</t>
+          <t>2026-09-01 20:33:08</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:24</t>
+          <t>2026-09-01 20:33:08</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 19:34:24</t>
+          <t>2026-09-01 20:33:08</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
